--- a/data/trans_bre/P44-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P44-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 23,33</t>
+          <t>-3,71; 23,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 0,27</t>
+          <t>-17,06; 1,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -2,53</t>
+          <t>-17,22; -1,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 234,47</t>
+          <t>-25,42; 234,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 5,19</t>
+          <t>-76,07; 18,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,36; -4,97</t>
+          <t>-31,61; -2,68</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 12,96</t>
+          <t>-7,48; 12,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,77; -5,52</t>
+          <t>-20,63; -5,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 6,18</t>
+          <t>-9,82; 6,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 167,0</t>
+          <t>-61,17; 155,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,31; -30,11</t>
+          <t>-88,3; -23,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 18,45</t>
+          <t>-23,43; 18,47</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 6,62</t>
+          <t>-8,85; 5,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 6,84</t>
+          <t>-8,44; 7,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-65,67; -4,49</t>
+          <t>-65,23; -4,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-65,2; 87,74</t>
+          <t>-65,14; 65,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 76,43</t>
+          <t>-65,61; 83,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,53; -13,9</t>
+          <t>-74,15; -11,65</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 4,56</t>
+          <t>-5,06; 4,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 4,5</t>
+          <t>-4,73; 5,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,6; -0,92</t>
+          <t>-27,71; -1,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 72,71</t>
+          <t>-51,49; 65,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 53,62</t>
+          <t>-44,15; 58,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,89; -3,16</t>
+          <t>-81,02; -5,45</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 7,27</t>
+          <t>-2,13; 6,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 3,16</t>
+          <t>-5,89; 2,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 4,16</t>
+          <t>-9,04; 3,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,95; 321,83</t>
+          <t>-30,98; 265,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-51,4; 50,46</t>
+          <t>-51,33; 43,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 17,8</t>
+          <t>-26,88; 13,34</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,14</t>
+          <t>3,71; 7,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,46</t>
+          <t>4,15; 8,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 14,42</t>
+          <t>-34,78; 15,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,64; 105,63</t>
+          <t>-57,33; 114,95</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,09</t>
+          <t>-4,25; 0,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; -2,13</t>
+          <t>-6,67; -2,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-44,2; -8,05</t>
+          <t>-44,06; -7,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 1,48</t>
+          <t>-39,3; 1,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-51,61; -20,28</t>
+          <t>-50,49; -21,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-71,7; -21,89</t>
+          <t>-66,65; -19,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P44-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P44-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-9,35</t>
+          <t>-8,07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-18,18%</t>
+          <t>-15,89%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 23,14</t>
+          <t>-4,23; 23,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 1,69</t>
+          <t>-16,72; 1,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -1,03</t>
+          <t>-15,96; 1,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 234,73</t>
+          <t>-26,49; 232,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-76,07; 18,61</t>
+          <t>-75,79; 15,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -2,68</t>
+          <t>-29,4; 1,58</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-6,37%</t>
+          <t>-3,82%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 12,35</t>
+          <t>-7,93; 12,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,63; -5,1</t>
+          <t>-21,41; -5,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 6,21</t>
+          <t>-10,19; 6,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 155,82</t>
+          <t>-58,9; 182,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,3; -23,67</t>
+          <t>-89,87; -26,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 18,47</t>
+          <t>-25,27; 19,79</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-39,21</t>
+          <t>-5,76</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-54,63%</t>
+          <t>-14,95%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 5,36</t>
+          <t>-8,62; 6,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 7,5</t>
+          <t>-8,96; 6,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-65,23; -4,16</t>
+          <t>-14,74; 3,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-65,14; 65,41</t>
+          <t>-63,01; 85,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,61; 83,2</t>
+          <t>-68,37; 69,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,15; -11,65</t>
+          <t>-35,67; 10,46</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-14,6</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-46,06%</t>
+          <t>-10,31%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 4,43</t>
+          <t>-5,01; 4,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 5,01</t>
+          <t>-4,67; 4,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,71; -1,73</t>
+          <t>-8,47; 2,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,49; 65,86</t>
+          <t>-51,37; 64,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 58,66</t>
+          <t>-43,27; 54,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,02; -5,45</t>
+          <t>-24,42; 8,8</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,77</t>
+          <t>-2,3</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,58%</t>
+          <t>-8,02%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 6,81</t>
+          <t>-1,97; 6,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 2,92</t>
+          <t>-5,89; 3,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 3,35</t>
+          <t>-8,36; 3,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 265,08</t>
+          <t>-27,68; 240,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 43,8</t>
+          <t>-51,02; 46,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 13,34</t>
+          <t>-24,46; 17,34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>-5,55</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-19,5%</t>
+          <t>-16,52%</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,31</t>
+          <t>3,62; 6,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,07</t>
+          <t>4,44; 8,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 15,23</t>
+          <t>-32,05; 15,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,33; 114,95</t>
+          <t>-54,43; 118,13</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-19,45</t>
+          <t>-6,04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-42,29%</t>
+          <t>-16,61%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,11</t>
+          <t>-4,37; 0,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -2,3</t>
+          <t>-6,93; -2,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-44,06; -7,24</t>
+          <t>-8,92; -3,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 1,52</t>
+          <t>-40,7; 2,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-50,49; -21,16</t>
+          <t>-52,03; -20,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-66,65; -19,54</t>
+          <t>-23,16; -9,55</t>
         </is>
       </c>
     </row>
